--- a/data/page_metadata_staging.xlsx
+++ b/data/page_metadata_staging.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\cdpet\Documents\Post School Coursework\Portfolio Website\portfolio-website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30C77263-45B2-4065-B821-A1737E3A588F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{734DFF03-A66E-442D-8B63-6865435ACB27}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-19200" yWindow="0" windowWidth="19200" windowHeight="15750" xr2:uid="{0F48850E-ADBC-4F08-8282-8BC2E517D1A7}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{0F48850E-ADBC-4F08-8282-8BC2E517D1A7}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="43">
   <si>
     <t>mlb_the_show</t>
   </si>
@@ -133,6 +133,27 @@
   </si>
   <si>
     <t>documentation, project setup, workflows</t>
+  </si>
+  <si>
+    <t>cfb_analysis</t>
+  </si>
+  <si>
+    <t>CFB 25 Analysis</t>
+  </si>
+  <si>
+    <t>https://github.com/cdpeters/cfb-analysis</t>
+  </si>
+  <si>
+    <t>https://cdpeters.github.io/cfb-analysis/</t>
+  </si>
+  <si>
+    <t>polars, altair, marimo, httpx</t>
+  </si>
+  <si>
+    <t>CFB 25 Roster Analysis</t>
+  </si>
+  <si>
+    <t>dataframe transformations, exploratory analysis, app</t>
   </si>
 </sst>
 </file>
@@ -623,6 +644,38 @@
         <v>27</v>
       </c>
     </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A5" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="B5" s="1">
+        <v>19</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>41</v>
+      </c>
+    </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="B10" s="6"/>
       <c r="E10" s="2"/>
@@ -702,8 +755,10 @@
     <hyperlink ref="E17" r:id="rId3" xr:uid="{9FA6B93E-A3A6-48EC-9C37-50B72ACF667C}"/>
     <hyperlink ref="I17" r:id="rId4" xr:uid="{E6B871A8-109A-4EE5-9BD7-70659F069CB1}"/>
     <hyperlink ref="E18" r:id="rId5" xr:uid="{AB90E9EA-AEFF-4EF8-A322-CAF589A0B570}"/>
+    <hyperlink ref="E5" r:id="rId6" xr:uid="{32F9DA12-88A9-412E-98BF-31586401C81E}"/>
+    <hyperlink ref="I5" r:id="rId7" xr:uid="{BB69B7E0-B372-49DC-98C3-8A88D7F44F40}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId6"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId8"/>
 </worksheet>
 </file>